--- a/docs/TEXTES-CONTEXTUELS-v1.xlsx
+++ b/docs/TEXTES-CONTEXTUELS-v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Textes contextuels" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes contextuels" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Textes contextuels'!$A$1:$D$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Textes contextuels'!$A$1:$D$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D187"/>
+  <dimension ref="A1:D166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Tu es arrivé le premier. Tu choisis ta place.</t>
+          <t>Tu es arrivé(e) le premier. Choisis ta place autour du feu.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Il n'y a que toi et les braises.</t>
+          <t>Pour le moment, il n'y a que toi et les braises.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Le feu part doucement. Comme toujours.</t>
+          <t>Patience... le feu part doucement, comme toujours.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Quelqu’un finira bien par sentir la fumée.</t>
+          <t>x</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Rien ne presse. Le bois est sec.</t>
+          <t>Le cercle est encore vide. Ça ne va pas durer.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Le cercle est vide. Ça ne durera pas.</t>
+          <t>Tu gardes le feu. C’est une responsabilité.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tu gardes le feu. C’est une responsabilité.</t>
+          <t>Profite : dans deux minutes, il y aura du monde.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Personne à qui parler, personne à qui mentir.</t>
+          <t>Le cercle se forme. En attente que le feu prenne !</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Profite : dans deux minutes, il y aura du monde.</t>
+          <t>Tout le monde est assis. Personne n’ose commencer.</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Le silence avant les rires. On y est.</t>
+          <t>Patience... tu as le temps de te griller un marshmallow.</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>le joueur est le seul dans le salon</t>
+          <t>au moins deux joueurs sont connectés</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Le cercle est formé. Il manque juste le signal.</t>
+          <t>Ça sent le bois et la compétition.</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Tout le monde est assis. Personne n’ose commencer.</t>
+          <t>Assis-toi sur ta souche et patiente mon ami(e).</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -740,7 +740,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tu as encore le temps de préparer une excuse.</t>
+          <t>On y est presque. Respire (mais pas la fumée).</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Ça sent le bois et la compétition.</t>
+          <t>C’est parti. On verra bien.</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>au moins deux joueurs sont connectés</t>
+          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Les places sont prises. Le feu attend.</t>
+          <t>Ta réponse est au chaud.</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>au moins deux joueurs sont connectés</t>
+          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Quelqu’un a forcément révisé. Ce n’est pas toi.</t>
+          <t>Les flammes ont entendu ta réponse.</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>au moins deux joueurs sont connectés</t>
+          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>On y est presque. Respire.</t>
+          <t>Voilà. Trop tard pour changer d’avis.</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>au moins deux joueurs sont connectés</t>
+          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Le plus dur, c’est d’attendre.</t>
+          <t>Reçu. Croise les doigts si tu veux.</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>au moins deux joueurs sont connectés</t>
+          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>C’est parti. On verra bien.</t>
+          <t>Ta voix est dans le pot commun.</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Ta réponse est au chaud.</t>
+          <t>Le temps passe vite autour du feu ! On se reconcentre.</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
+          <t>le chrono est tombé sans réponse du joueur</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Enregistré. Plus qu’à attendre.</t>
+          <t>Rien reçu... Parle plus fort la prochaine fois.</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
+          <t>le chrono est tombé sans réponse du joueur</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Voilà. Trop tard pour changer d’avis.</t>
+          <t>Bah alors ? Tu t'es endormi(e) au coin du feu ?</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
+          <t>le chrono est tombé sans réponse du joueur</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Reçu. Croise les doigts si tu veux.</t>
+          <t>Ouhlala... t'es parti(e) au petit coin ?</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
+          <t>le chrono est tombé sans réponse du joueur</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Ta voix est dans le pot commun.</t>
+          <t>Bien vu l'ami(e).</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>la réponse est enregistrée, la manche n’est pas révélée</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Le temps a filé. Ça arrive.</t>
+          <t>C’était ça.</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>le chrono est tombé sans réponse du joueur</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Rien envoyé cette fois. La prochaine est à toi.</t>
+          <t>Solide.</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>le chrono est tombé sans réponse du joueur</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Trop tard — mais ça ne coûte rien.</t>
+          <t>Tu le savais. Ça se voit.</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>le chrono est tombé sans réponse du joueur</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Manche blanche. On repart entier.</t>
+          <t>Propre.</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>le chrono est tombé sans réponse du joueur</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bien vu.</t>
+          <t>Sans trembler.</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>C’était ça.</t>
+          <t>Exactement ça.</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Solide.</t>
+          <t>Tranquille.</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse, sans être le plus rapide de la manche ni en série</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Tu savais. Ça se voit.</t>
+          <t>L'un(e) des plus rapide du cercle. Ziouuuum......</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse ET plus rapide de la manche (drapeau `fastest` du serveur)</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Propre.</t>
+          <t>C'est vif, et juste. Telle la flèche de Robin des bois.</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse ET plus rapide de la manche (drapeau `fastest` du serveur)</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Sans trembler.</t>
+          <t>Tu as répondu avant que les autres finissent de lire.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse ET plus rapide de la manche (drapeau `fastest` du serveur)</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Exactement ça.</t>
+          <t>Mère Nature est fière de toi.</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse ET plus rapide de la manche (drapeau `fastest` du serveur)</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Tranquille.</t>
+          <t>Le feu crépite de joie en te voyant jouer !</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse, sans supplément de rapidité ni série</t>
+          <t>bonne réponse ET plus rapide de la manche (drapeau `fastest` du serveur)</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Le plus rapide du cercle. Personne n’a vu passer ta main.</t>
+          <t>{serie} d’affilée. Attention à ne pas t'enflammer !</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET plus rapide de la manche (speed inclut le supplément)</t>
+          <t>bonne réponse ET série de 2 ou plus</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Premier, et juste. Ça ne s’improvise pas.</t>
+          <t>Toujours pas de faute. {serie} de suite.</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET plus rapide de la manche (speed inclut le supplément)</t>
+          <t>bonne réponse ET série de 2 ou plus</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Tu as répondu avant que les autres finissent de lire.</t>
+          <t>{serie} bonnes réponses enchaînées. Le feu t'admire.</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET plus rapide de la manche (speed inclut le supplément)</t>
+          <t>bonne réponse ET série de 2 ou plus</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Le doigt plus vite que la pensée — sauf que c’était bon.</t>
+          <t>Une série enflammée ! {serie} et ça continue.</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET plus rapide de la manche (speed inclut le supplément)</t>
+          <t>bonne réponse ET série de 2 ou plus</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Réflexe de braconnier.</t>
+          <t>{serie} à la suite : on ne t'arrête plus.</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET plus rapide de la manche (speed inclut le supplément)</t>
+          <t>bonne réponse ET série de 2 ou plus</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>{serie} d’affilée. Tu commences à faire peur.</t>
+          <t>Ouch ! Tu t'es brûlé(e) sur celle-ci.</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET série de 2 ou plus</t>
+          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Toujours pas fautif. {serie} de suite.</t>
+          <t>Aïe raté... ça fait plus mal qu'une écharde.</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET série de 2 ou plus</t>
+          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>{serie} bonnes réponses enchaînées. On te regarde.</t>
+          <t>À côté... Touche du bois pour la prochaine.</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET série de 2 ou plus</t>
+          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>La série tient. {serie} et ça continue.</t>
+          <t>Non non non... le feu va s'éteindre.</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET série de 2 ou plus</t>
+          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>{serie} d’affilée : quelqu’un devrait t’arrêter.</t>
+          <t>Manqué. Chut, personne n’a rien vu.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>bonne réponse ET série de 2 ou plus</t>
+          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Raté — mais ça ne coûte rien.</t>
+          <t>Ce n’était pas ça. Ça arrive aux meilleurs.</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Pas cette fois. Rien de perdu.</t>
+          <t>Dommage... Ne laisse pas tes espoirs se consumer !</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>À côté. La prochaine est neuve.</t>
+          <t>Celle-là s’est jouée sans toi. Il va falloir envoyer du bois pour revenir.</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
+          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Non. On efface et on repart.</t>
+          <t>Tu arrives : le cercle avait déjà commencé. Le feu n'attend pas.</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
+          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Manqué. Personne n’a rien vu.</t>
+          <t>Tu entres en jeu maintenant petite allumette.</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
+          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>Ce n’était pas ça. Ça arrive aux meilleurs.</t>
+          <t>Wow ! Dans le mille.</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
+          <t>palier « exact » : la valeur donnée est exactement la cible</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Zéro pointé, zéro dégât.</t>
+          <t>Le cercle t'applaudit !</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>mauvaise réponse (aucune pénalité : zéro point, pas moins)</t>
+          <t>palier « exact » : la valeur donnée est exactement la cible</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Ta réponse est bien partie. On attend le verdict.</t>
+          <t>La précision c'est ton dada !</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>le joueur a répondu, son résultat n’est pas encore arrivé</t>
+          <t>palier « exact » : la valeur donnée est exactement la cible</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>C’est enregistré. Le résultat arrive.</t>
+          <t>Tu as visé juste au chiffre près.</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>le joueur a répondu, son résultat n’est pas encore arrivé</t>
+          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Tout est en ordre de ton côté.</t>
+          <t>Exact ! (enfin quasi)</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>le joueur a répondu, son résultat n’est pas encore arrivé</t>
+          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Patience : la manche se termine.</t>
+          <t>T'es plutôt doué !</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>le joueur a répondu, son résultat n’est pas encore arrivé</t>
+          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Celle-là s’est jouée sans toi. La prochaine est à toi.</t>
+          <t>À une brindille de mettre le feu !</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
+          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Tu arrives : le cercle avait déjà commencé.</t>
+          <t>Tout près. Bien vu.</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
+          <t>palier « proche » : à 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Manche manquée, soirée intacte.</t>
+          <t>Presque pile. On prend.</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
+          <t>palier « proche » : à 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Rien de perdu — tu entres maintenant.</t>
+          <t>Tu avais l’ordre de grandeur et la finesse.</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>le joueur n’a pas participé à cette manche (arrivé après le lancement)</t>
+          <t>palier « proche » : à 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>{places} de gagnées. Continue comme ça.</t>
+          <t>Belle visée.</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &gt; 0</t>
+          <t>palier « proche » : à 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Tu remontes de {places}. Ça se sent.</t>
+          <t>Pas loin du tout.</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &gt; 0</t>
+          <t>palier « proche » : à 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>{places} places grignotées.</t>
+          <t>Dans la bonne zone.</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &gt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>{places} de plus au compteur des places.</t>
+          <t>Pas mal visé.</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &gt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Ça monte : {places} de gagnées.</t>
+          <t>L’ordre de grandeur y est.</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &gt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Les autres avancent. Toi aussi, bientôt.</t>
+          <t>Correct, sans être chirurgical.</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &lt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Ça bouscule derrière. Rien d’irréversible.</t>
+          <t>Tu n’étais pas perdu.</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &lt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Un peu de terrain perdu. Le feu brûle encore.</t>
+          <t>La direction était bonne.</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &lt; 0</t>
+          <t>palier « correct » : à 20 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Le cercle se resserre autour de toi.</t>
+          <t>Un peu large, mais tu y étais.</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &lt; 0</t>
+          <t>palier « loin » : à 30 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Ça bouge devant. Rien n’est joué.</t>
+          <t>Pas tout à fait. L’idée était là.</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>placesDelta &lt; 0</t>
+          <t>palier « loin » : à 30 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Dans le mille. Presque suspect.</t>
+          <t>Ça s’éloigne, sans se perdre.</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
+          <t>palier « loin » : à 30 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Tu as visé juste au chiffre près.</t>
+          <t>Généreux dans l’estimation.</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
+          <t>palier « loin » : à 30 % de la cible</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Exact, ou tout comme.</t>
+          <t>Loin, mais le moins loin de tous. Ça compte.</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
+          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Personne ne fait mieux que ça.</t>
+          <t>Personne n’a fait mieux. C’est déjà une victoire.</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
+          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Pile. Sans hésiter.</t>
+          <t>Le plus proche du cercle — de loin, mais le plus proche.</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>palier « mille » : à 2 % de la cible, ou à une unité près</t>
+          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Tout près. Bien vu.</t>
+          <t>Tout le monde s’est perdu. Toi, un peu moins.</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>À un cheveu. Solide.</t>
+          <t>Pas dans le mille, mais devant les autres.</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Presque pile. On prend.</t>
+          <t>Là, on est loin. Vraiment loin.</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Tu avais l’ordre de grandeur et la finesse.</t>
+          <t>Tu as dû missclick.</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Belle visée.</t>
+          <t>Ouch ! Tu t'es brûlé(e) sur celle-ci.</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Pas loin du tout.</t>
+          <t>On ne parlait peut-être pas de la même chose.</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>palier « proche » : à 10 % de la cible</t>
+          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Dans la bonne zone.</t>
+          <t>On va faire comme s'il ne s'était rien passé...</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Pas mal visé.</t>
+          <t>T'es avec le cercle !</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>L’ordre de grandeur y est.</t>
+          <t>Tu sais où souffle le vent ! Et le feu aime le vent.</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Correct, sans être chirurgical.</t>
+          <t>Le cercle pensait comme toi.</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Tu n’étais pas perdu.</t>
+          <t>Peu importe si c'est ce que tu penses vraiment, t'es là où il faut.</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>La direction était bonne.</t>
+          <t>Dans le camp le plus fourni.</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>palier « correct » : à 20 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Un peu large, mais tu y étais.</t>
+          <t>Bien vu : le cercle t’a suivi.</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>palier « loin » : à 30 % de la cible</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Pas tout à fait. L’idée était là.</t>
+          <t>Seul contre le cercle. Courageux.</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>palier « loin » : à 30 % de la cible</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Ça s’éloigne — sans se perdre.</t>
+          <t>Le cercle en a décidé autrement. Montre lui de quel bois tu te chauffes.</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>palier « loin » : à 30 % de la cible</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Tu visais le bon continent.</t>
+          <t>À contre-courant.</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>palier « loin » : à 30 % de la cible</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Généreux dans l’estimation.</t>
+          <t>C'est comme se sentir seul... mais en pire.</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>palier « loin » : à 30 % de la cible</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Loin, mais le moins loin de tous. Ça compte.</t>
+          <t>Minoritaire, et assumé. Tu vas te refaire.</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Personne n’a fait mieux. C’est déjà une victoire.</t>
+          <t>Le cercle a penché ailleurs.</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Le plus proche du cercle — de loin, mais le plus proche.</t>
+          <t>Ta voix compte. (Je le pense vraiment)</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
+          <t>vote en mode sondage : personne ne gagne</t>
         </is>
       </c>
     </row>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Tout le monde s’est perdu. Toi, un peu moins.</t>
+          <t>C’est noté. Sans enjeu, juste ton opinion, et je l'apprécie.</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
+          <t>vote en mode sondage : personne ne gagne</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Pas dans le mille, mais devant les autres.</t>
+          <t>Merci ! Le cercle t’a entendu.</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, mais le plus proche : le bonus de 400</t>
+          <t>vote en mode sondage : personne ne gagne</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Là, on est loin. Vraiment loin.</t>
+          <t>Un avis, pas un pari.</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
+          <t>vote en mode sondage : personne ne gagne</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Autre ordre de grandeur. Ça arrive.</t>
+          <t>{rang} du cercle. Tu peux être fier(e) !</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
+          <t>le joueur termine dans les trois premiers</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Complètement à côté — et ça ne coûte rien.</t>
+          <t>Sur le podium. C’était mérité.</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
+          <t>le joueur termine dans les trois premiers</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>On ne parlait peut-être pas de la même chose.</t>
+          <t>{rang} — Jubile devant les autres, ça n'arrivera peut-être plus.</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
+          <t>le joueur termine dans les trois premiers</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Hardi, mais non.</t>
+          <t>{rang}. L'une des légendes du cercle. Bravo</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>au-delà de 30 % de la cible, et pas le plus proche : zéro point</t>
+          <t>le joueur termine dans les trois premiers</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Avec la salle. Tu la lis bien.</t>
+          <t>{rang}. La soirée n’était pas perdue. Le cercle se souvient.</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur est classé hors podium</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Majoritaire. Tu sais où souffle le vent.</t>
+          <t>Tu finis {rang}. Tu reviendras plus fort(e).</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur est classé hors podium</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Le groupe pensait comme toi.</t>
+          <t>{rang}, on acclame le podium et on prie pour les perdants</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur est classé hors podium</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Tu as senti le cercle.</t>
+          <t>{rang}, et une revanche à prendre.</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur est classé hors podium</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Dans le camp le plus fourni.</t>
+          <t>Tu es resté jusqu’au bout. C’est déjà beaucoup.</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur termine dernier, ou sans point</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Bien vu : la salle t’a suivi.</t>
+          <t>Le classement dit une chose, la soirée en dit une autre.</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le joueur termine dernier, ou sans point</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Seul contre le cercle. Ça a du panache.</t>
+          <t>Une prochaine fois. Le feu ne s’éteint pas.</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le joueur termine dernier, ou sans point</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Le groupe en a décidé autrement. Aucun point retiré.</t>
+          <t>Dernier au tableau, présent au cercle.</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2710,407 +2710,407 @@
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le joueur termine dernier, ou sans point</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>À contre-courant. Ce n’est pas une faute.</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>vote noté, le joueur est minoritaire</t>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>Tout le cercle a trouvé. Trop facile ?</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Tu avais peut-être raison. Ça ne compte juste pas.</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>vote noté, le joueur est minoritaire</t>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle est bon. Trop bon ?</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Minoritaire, et assumé.</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>vote noté, le joueur est minoritaire</t>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>Unanimité. La question était trop tendre.</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Le cercle a penché ailleurs.</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>vote noté, le joueur est minoritaire</t>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>Sans faute, tout le monde.</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>Ta voix compte. Pas en points, en avis.</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle au complet a visé juste.</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>C’est noté. Sans enjeu, juste ton opinion.</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>Personne. Absolument personne... ça c'est un cercle uni !</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>Merci — la salle t’a entendu.</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle entier est passé à côté.</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Un avis, pas un pari.</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>Zéro bonne réponse. La question a gagné.</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>{rang} du cercle. Tu peux te resservir.</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>Toute la salle dans le mur, ensemble.</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Sur le podium. C’était mérité.</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>Pas un seul. C’est presque beau.</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>{rang} — garde-le pour la prochaine fois.</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>Le piège a fonctionné. La majorité est tombée dedans.</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>{rang}. La soirée est à toi.</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>La salle a choisi la mauvaise porte, en groupe.</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>{rang}. La soirée n’était pas perdue.</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>le joueur est classé hors podium</t>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>Belle embuscade : le cercle s’est fait avoir.</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>Tu finis {rang}. Il y a des podiums plus faciles.</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>le joueur est classé hors podium</t>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>La plupart se sont brûlés. Bravo aux autres !</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>{rang} — largement de quoi revenir.</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>le joueur est classé hors podium</t>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>Piégés, et en nombre.</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>{rang}, et une revanche à prendre.</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>le joueur est classé hors podium</t>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>Presque tout le monde a trouvé.</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Tu es resté jusqu’au bout. C’est déjà beaucoup.</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dernier, ou sans point</t>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Quasi-unanimité. Un ou deux distraits.</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>Le classement dit une chose, la soirée en dit une autre.</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dernier, ou sans point</t>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle était sûr de lui, à raison.</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Prochaine fois. Le feu ne s’éteint pas.</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dernier, ou sans point</t>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>À une poignée près, tout le monde.</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Dernier au tableau, présent au cercle.</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dernier, ou sans point</t>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle est coupé en deux.</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Tout le cercle a trouvé. Trop facile ?</t>
+          <t>Wow ! Égalité parfaite.</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Personne ne s’est trompé. Chapeau collectif.</t>
+          <t>Le cercle est partagé...</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Unanimité. La question était trop tendre.</t>
+          <t>Il y a une option qui devrait finir au feu.</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Sans faute, tout le monde.</t>
+          <t>Il y avait une option de trop on dirait.</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Le cercle au complet a visé juste.</t>
+          <t>Une proposition délaissée par le cercle.</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Personne. Absolument personne.</t>
+          <t>Le cercle n'est pas dûpe face à cette option bancale.</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Le cercle entier est passé à côté.</t>
+          <t>Le cercle est d’accord. C’est rare.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Zéro bonne réponse. La question a gagné.</t>
+          <t>Consensus écrasant.</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Toute la salle dans le mur, ensemble.</t>
+          <t>Presque tout le cercle est du même avis.</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Pas un seul. C’est presque beau.</t>
+          <t>Le feu s'intensifie en voyant une telle unité !</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Le piège a fonctionné. La majorité est tombée dedans.</t>
+          <t>Le cercle hésite. Deux camps à égalité.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>La salle a choisi la mauvaise porte, en groupe.</t>
+          <t>Le feu brûle de bonheur en voyant cette compétition !</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Belle embuscade : le cercle s’est fait avoir.</t>
+          <t>La cercle est coupé en deux... ça fait des demi-cercles du coup.</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>La fausse réponse était plus séduisante.</t>
+          <t>Mais qui a gagné en fait ?</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Piégés, et en nombre.</t>
+          <t>Un cercle de qualité !</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Presque tout le monde a trouvé.</t>
+          <t>Ensemble, le cercle a ajusté sa mire !</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Quasi-unanimité. Un ou deux distraits.</t>
+          <t>Le cercle a envoyé du bois sur celle-ci.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Le cercle était sûr de lui — à raison.</t>
+          <t>La sagesse de la foule, pour une fois.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>À une poignée près, tout le monde.</t>
+          <t>Le cercle s’est trompé d’échelle.</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Le cercle est coupé en deux.</t>
+          <t>Tout le monde a visé beaucoup trop loin.</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Égalité parfaite. Personne ne tranche.</t>
+          <t>Une partie du cercle était hors sujet.</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Deux camps, pas un de plus que l’autre.</t>
+          <t>Collectivement à côté de la plaque.</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>La salle est partagée, exactement.</t>
+          <t>Une seule personne talentueuse dans le cercle on dirait.</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Une réponse que personne n’a voulue.</t>
+          <t>Une estimation au millimètre dans le lot. Chapeau bas !</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Il y avait une option de trop.</t>
+          <t>Il y a un expert dans le cercle. Gardons-le à l'œil !</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Une proposition délaissée par tout le monde.</t>
+          <t>Quelqu’un savait, et c'est tout à son honneur.</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Personne n’a mordu à celle-là.</t>
+          <t>Le cercle est parti se promener sur cette estimation on dirait.</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>La salle est d’accord. C’est rare.</t>
+          <t>Alors... le but du jeu c'est d'être le plus proche de la réponse, pas le plus loin.</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Consensus écrasant.</t>
+          <t>Le cercle est resté loin du compte. Il va falloir songer à toucher du bois un peu.</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Presque tout le cercle du même avis.</t>
+          <t>Ouch ! Le feu se sent bien seul sur celle-là.</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Peu de débat sur celle-là.</t>
+          <t>Voici un podium de qualité ! (et le reste du cercle aussi vous avez du talent)</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Le cercle hésite. Deux camps à égalité.</t>
+          <t>La feu a rendu son verdict ! Bravo à notre grand vainqueur !</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Aucune majorité claire. Ça va discuter.</t>
+          <t>Trois en haut, et tout le monde danse autour du feu.</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>La salle est coupée en deux.</t>
+          <t>Tout feu tout flamme ces 3 gagnants ! (et les autres vous êtes chauds aussi !)</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
@@ -3790,432 +3790,12 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="4" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>Personne ne l’emporte vraiment.</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D167" s="5" t="inlineStr">
-        <is>
-          <t>vote : les deux premières options à une voix près</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="4" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
-        <is>
-          <t>La moyenne du cercle tombe presque juste.</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>Ensemble, la salle avait vu juste.</t>
-        </is>
-      </c>
-      <c r="C169" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D169" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="4" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" s="5" t="inlineStr">
-        <is>
-          <t>Le groupe, collectivement, ne s’est pas trompé.</t>
-        </is>
-      </c>
-      <c r="C170" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D170" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="4" t="n">
-        <v>170</v>
-      </c>
-      <c r="B171" s="5" t="inlineStr">
-        <is>
-          <t>La sagesse de la foule, pour une fois.</t>
-        </is>
-      </c>
-      <c r="C171" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="n">
-        <v>171</v>
-      </c>
-      <c r="B172" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle s’est trompé d’échelle.</t>
-        </is>
-      </c>
-      <c r="C172" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="5" t="inlineStr">
-        <is>
-          <t>Tout le monde a visé beaucoup trop haut.</t>
-        </is>
-      </c>
-      <c r="C173" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D173" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="5" t="inlineStr">
-        <is>
-          <t>La salle entière était hors sujet.</t>
-        </is>
-      </c>
-      <c r="C174" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D174" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="n">
-        <v>174</v>
-      </c>
-      <c r="B175" s="5" t="inlineStr">
-        <is>
-          <t>Collectivement à côté de la plaque.</t>
-        </is>
-      </c>
-      <c r="C175" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D175" s="5" t="inlineStr">
-        <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="B176" s="5" t="inlineStr">
-        <is>
-          <t>Quelqu’un est tombé pile. Sans calculer, on parie.</t>
-        </is>
-      </c>
-      <c r="C176" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D176" s="5" t="inlineStr">
-        <is>
-          <t>la meilleure estimation est à moins de 2 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="4" t="n">
-        <v>176</v>
-      </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>Une estimation au millimètre dans le lot.</t>
-        </is>
-      </c>
-      <c r="C177" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D177" s="5" t="inlineStr">
-        <is>
-          <t>la meilleure estimation est à moins de 2 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="n">
-        <v>177</v>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>Il y a un expert dans la salle.</t>
-        </is>
-      </c>
-      <c r="C178" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D178" s="5" t="inlineStr">
-        <is>
-          <t>la meilleure estimation est à moins de 2 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="4" t="n">
-        <v>178</v>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>Quelqu’un savait, manifestement.</t>
-        </is>
-      </c>
-      <c r="C179" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D179" s="5" t="inlineStr">
-        <is>
-          <t>la meilleure estimation est à moins de 2 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" s="5" t="inlineStr">
-        <is>
-          <t>Personne n’a approché. La question a gagné.</t>
-        </is>
-      </c>
-      <c r="C180" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D180" s="5" t="inlineStr">
-        <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" s="5" t="inlineStr">
-        <is>
-          <t>Pas une estimation dans la bonne zone.</t>
-        </is>
-      </c>
-      <c r="C181" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D181" s="5" t="inlineStr">
-        <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle est resté loin du compte.</t>
-        </is>
-      </c>
-      <c r="C182" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D182" s="5" t="inlineStr">
-        <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="4" t="n">
-        <v>182</v>
-      </c>
-      <c r="B183" s="5" t="inlineStr">
-        <is>
-          <t>Aucune approche sérieuse.</t>
-        </is>
-      </c>
-      <c r="C183" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
-        <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="4" t="n">
-        <v>183</v>
-      </c>
-      <c r="B184" s="5" t="inlineStr">
-        <is>
-          <t>Voilà le cercle au complet.</t>
-        </is>
-      </c>
-      <c r="C184" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D184" s="5" t="inlineStr">
-        <is>
           <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="4" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" s="5" t="inlineStr">
-        <is>
-          <t>La soirée a rendu son verdict.</t>
-        </is>
-      </c>
-      <c r="C185" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D185" s="5" t="inlineStr">
-        <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
-        <is>
-          <t>Trois en haut, tout le monde autour du feu.</t>
-        </is>
-      </c>
-      <c r="C186" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="n">
-        <v>186</v>
-      </c>
-      <c r="B187" s="5" t="inlineStr">
-        <is>
-          <t>Le classement est tombé.</t>
-        </is>
-      </c>
-      <c r="C187" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D187" s="5" t="inlineStr">
-        <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D187"/>
+  <autoFilter ref="A1:D166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/TEXTES-CONTEXTUELS-v1.xlsx
+++ b/docs/TEXTES-CONTEXTUELS-v1.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textes contextuels" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Textes contextuels'!$A$1:$D$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Textes contextuels'!$A$1:$D$186</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D166"/>
+  <dimension ref="A1:D186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>T'es avec le cercle !</t>
+          <t>Personne n’a pensé comme toi. C’est original, ça ne rapporte rien.</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : personne d’autre n’a donné ce mot</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Tu sais où souffle le vent ! Et le feu aime le vent.</t>
+          <t>Ton mot n’a trouvé personne. Le cercle pensait ailleurs.</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : personne d’autre n’a donné ce mot</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Le cercle pensait comme toi.</t>
+          <t>Seul de ton avis. Ça arrive aux meilleurs.</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : personne d’autre n’a donné ce mot</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Peu importe si c'est ce que tu penses vraiment, t'es là où il faut.</t>
+          <t>Bien vu, mais tout seul — et ici, seul ne compte pas.</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : personne d’autre n’a donné ce mot</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Dans le camp le plus fourni.</t>
+          <t>Le mot que tout le monde attendait. Tu l’as trouvé.</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : le joueur est dans le groupe le plus nombreux</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Bien vu : le cercle t’a suivi.</t>
+          <t>En plein dans la tête du cercle.</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est dans un camp gagnant</t>
+          <t>le lien : le joueur est dans le groupe le plus nombreux</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Seul contre le cercle. Courageux.</t>
+          <t>Le groupe le plus nombreux, et tu en es.</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur est dans le groupe le plus nombreux</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Le cercle en a décidé autrement. Montre lui de quel bois tu te chauffes.</t>
+          <t>Tu penses comme la majorité. Ce soir, c’est un talent.</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur est dans le groupe le plus nombreux</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>À contre-courant.</t>
+          <t>Vous êtes {taille} à y avoir pensé.</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur partage son mot, hors du groupe de tête</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>C'est comme se sentir seul... mais en pire.</t>
+          <t>Ton mot a trouvé du monde. Pas la foule, mais du monde.</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur partage son mot, hors du groupe de tête</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Minoritaire, et assumé. Tu vas te refaire.</t>
+          <t>Partagé — ce n’était donc pas si tiré par les cheveux.</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur partage son mot, hors du groupe de tête</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Le cercle a penché ailleurs.</t>
+          <t>Un petit groupe s’est formé autour de toi.</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2390,167 +2390,167 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>vote noté, le joueur est minoritaire</t>
+          <t>le lien : le joueur partage son mot, hors du groupe de tête</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>Ta voix compte. (Je le pense vraiment)</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle n’a eu qu’une seule idée.</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>le lien : la moitié du cercle au moins a donné le même mot</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>C’est noté. Sans enjeu, juste ton opinion, et je l'apprécie.</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Une évidence pour presque tout le monde.</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>le lien : la moitié du cercle au moins a donné le même mot</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>Merci ! Le cercle t’a entendu.</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>Rarement vu autant de monde d’accord.</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>le lien : la moitié du cercle au moins a donné le même mot</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>Un avis, pas un pari.</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>vote en mode sondage : personne ne gagne</t>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>Un seul mot, et il a rassemblé.</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>le lien : la moitié du cercle au moins a donné le même mot</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>{rang} du cercle. Tu peux être fier(e) !</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>Personne n’a pensé comme personne.</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>le lien : personne n’a partagé son mot, tous les groupes sont seuls</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Sur le podium. C’était mérité.</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>Autant de mots que de joueurs. Belle dispersion.</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>le lien : personne n’a partagé son mot, tous les groupes sont seuls</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>{rang} — Jubile devant les autres, ça n'arrivera peut-être plus.</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle est parti dans toutes les directions.</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>le lien : personne n’a partagé son mot, tous les groupes sont seuls</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>{rang}. L'une des légendes du cercle. Bravo</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>le joueur termine dans les trois premiers</t>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>Aucun mot en commun. Ça n’arrive pas souvent.</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>le lien : personne n’a partagé son mot, tous les groupes sont seuls</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>{rang}. La soirée n’était pas perdue. Le cercle se souvient.</t>
+          <t>T'es avec le cercle !</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>le joueur est classé hors podium</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Tu finis {rang}. Tu reviendras plus fort(e).</t>
+          <t>Tu sais où souffle le vent ! Et le feu aime le vent.</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>le joueur est classé hors podium</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>{rang}, on acclame le podium et on prie pour les perdants</t>
+          <t>Le cercle pensait comme toi.</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>le joueur est classé hors podium</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>{rang}, et une revanche à prendre.</t>
+          <t>Peu importe si c'est ce que tu penses vraiment, t'es là où il faut.</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>le joueur est classé hors podium</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Tu es resté jusqu’au bout. C’est déjà beaucoup.</t>
+          <t>Dans le camp le plus fourni.</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>le joueur termine dernier, ou sans point</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Le classement dit une chose, la soirée en dit une autre.</t>
+          <t>Bien vu : le cercle t’a suivi.</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>le joueur termine dernier, ou sans point</t>
+          <t>vote noté, le joueur est dans un camp gagnant</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Une prochaine fois. Le feu ne s’éteint pas.</t>
+          <t>Seul contre le cercle. Courageux.</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>le joueur termine dernier, ou sans point</t>
+          <t>vote noté, le joueur est minoritaire</t>
         </is>
       </c>
     </row>
@@ -2700,417 +2700,417 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
+          <t>Le cercle en a décidé autrement. Montre lui de quel bois tu te chauffes.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>vote noté, le joueur est minoritaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>À contre-courant.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>vote noté, le joueur est minoritaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>C'est comme se sentir seul... mais en pire.</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>vote noté, le joueur est minoritaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>Minoritaire, et assumé. Tu vas te refaire.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>vote noté, le joueur est minoritaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>Le cercle a penché ailleurs.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>vote noté, le joueur est minoritaire</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>Ta voix compte. (Je le pense vraiment)</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>vote en mode sondage : personne ne gagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>C’est noté. Sans enjeu, juste ton opinion, et je l'apprécie.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>vote en mode sondage : personne ne gagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>Merci ! Le cercle t’a entendu.</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>vote en mode sondage : personne ne gagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>Un avis, pas un pari.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>vote en mode sondage : personne ne gagne</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>{rang} du cercle. Tu peux être fier(e) !</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dans les trois premiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>Sur le podium. C’était mérité.</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dans les trois premiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>{rang} — Jubile devant les autres, ça n'arrivera peut-être plus.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dans les trois premiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>{rang}. L'une des légendes du cercle. Bravo</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dans les trois premiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>{rang}. La soirée n’était pas perdue. Le cercle se souvient.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>le joueur est classé hors podium</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>Tu finis {rang}. Tu reviendras plus fort(e).</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>le joueur est classé hors podium</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>{rang}, on acclame le podium et on prie pour les perdants</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>le joueur est classé hors podium</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>{rang}, et une revanche à prendre.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>le joueur est classé hors podium</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>Tu es resté jusqu’au bout. C’est déjà beaucoup.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dernier, ou sans point</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>Le classement dit une chose, la soirée en dit une autre.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dernier, ou sans point</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>Une prochaine fois. Le feu ne s’éteint pas.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>le joueur termine dernier, ou sans point</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
           <t>Dernier au tableau, présent au cercle.</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Joueur (téléphone)</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Joueur (téléphone)</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>le joueur termine dernier, ou sans point</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="4" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="5" t="inlineStr">
-        <is>
-          <t>Tout le cercle a trouvé. Trop facile ?</t>
-        </is>
-      </c>
-      <c r="C113" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D113" s="5" t="inlineStr">
-        <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="4" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle est bon. Trop bon ?</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="5" t="inlineStr">
-        <is>
-          <t>Unanimité. La question était trop tendre.</t>
-        </is>
-      </c>
-      <c r="C115" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D115" s="5" t="inlineStr">
-        <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="4" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="5" t="inlineStr">
-        <is>
-          <t>Sans faute, tout le monde.</t>
-        </is>
-      </c>
-      <c r="C116" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D116" s="5" t="inlineStr">
-        <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="4" t="n">
-        <v>116</v>
-      </c>
-      <c r="B117" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle au complet a visé juste.</t>
-        </is>
-      </c>
-      <c r="C117" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="4" t="n">
-        <v>117</v>
-      </c>
-      <c r="B118" s="5" t="inlineStr">
-        <is>
-          <t>Personne. Absolument personne... ça c'est un cercle uni !</t>
-        </is>
-      </c>
-      <c r="C118" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D118" s="5" t="inlineStr">
-        <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="4" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle entier est passé à côté.</t>
-        </is>
-      </c>
-      <c r="C119" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>Zéro bonne réponse. La question a gagné.</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>Toute la salle dans le mur, ensemble.</t>
-        </is>
-      </c>
-      <c r="C121" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="4" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>Pas un seul. C’est presque beau.</t>
-        </is>
-      </c>
-      <c r="C122" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>Le piège a fonctionné. La majorité est tombée dedans.</t>
-        </is>
-      </c>
-      <c r="C123" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>La salle a choisi la mauvaise porte, en groupe.</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>Belle embuscade : le cercle s’est fait avoir.</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="4" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>La plupart se sont brûlés. Bravo aux autres !</t>
-        </is>
-      </c>
-      <c r="C126" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>Piégés, et en nombre.</t>
-        </is>
-      </c>
-      <c r="C127" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="4" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>Presque tout le monde a trouvé.</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>Quasi-unanimité. Un ou deux distraits.</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="4" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle était sûr de lui, à raison.</t>
-        </is>
-      </c>
-      <c r="C130" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="4" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="5" t="inlineStr">
-        <is>
-          <t>À une poignée près, tout le monde.</t>
-        </is>
-      </c>
-      <c r="C131" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>au moins neuf réponses sur dix sont justes</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="4" t="n">
-        <v>131</v>
-      </c>
-      <c r="B132" s="5" t="inlineStr">
-        <is>
-          <t>Le cercle est coupé en deux.</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Wow ! Égalité parfaite.</t>
+          <t>Tout le cercle a trouvé. Trop facile ?</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Le cercle est partagé...</t>
+          <t>Le cercle est bon. Trop bon ?</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>les deux options de tête se tiennent à une voix</t>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Il y a une option qui devrait finir au feu.</t>
+          <t>Unanimité. La question était trop tendre.</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Il y avait une option de trop on dirait.</t>
+          <t>Sans faute, tout le monde.</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Une proposition délaissée par le cercle.</t>
+          <t>Le cercle au complet a visé juste.</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>tout le monde a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Le cercle n'est pas dûpe face à cette option bancale.</t>
+          <t>Personne. Absolument personne... ça c'est un cercle uni !</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>une option n’a recueilli aucune voix</t>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Le cercle est d’accord. C’est rare.</t>
+          <t>Le cercle entier est passé à côté.</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Consensus écrasant.</t>
+          <t>Zéro bonne réponse. La question a gagné.</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Presque tout le cercle est du même avis.</t>
+          <t>Toute la salle dans le mur, ensemble.</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Le feu s'intensifie en voyant une telle unité !</t>
+          <t>Pas un seul. C’est presque beau.</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>vote : une option dépasse huit voix sur dix</t>
+          <t>personne n’a trouvé (&gt;= 5 réponses)</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Le cercle hésite. Deux camps à égalité.</t>
+          <t>Le piège a fonctionné. La majorité est tombée dedans.</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Le feu brûle de bonheur en voyant cette compétition !</t>
+          <t>La salle a choisi la mauvaise porte, en groupe.</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>La cercle est coupé en deux... ça fait des demi-cercles du coup.</t>
+          <t>Belle embuscade : le cercle s’est fait avoir.</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Mais qui a gagné en fait ?</t>
+          <t>La plupart se sont brûlés. Bravo aux autres !</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>vote : les deux premières options à une voix près</t>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Un cercle de qualité !</t>
+          <t>Piégés, et en nombre.</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+          <t>une mauvaise option a recueilli plus de voix que la bonne</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Ensemble, le cercle a ajusté sa mire !</t>
+          <t>Presque tout le monde a trouvé.</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Le cercle a envoyé du bois sur celle-ci.</t>
+          <t>Quasi-unanimité. Un ou deux distraits.</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>La sagesse de la foule, pour une fois.</t>
+          <t>Le cercle était sûr de lui, à raison.</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Le cercle s’est trompé d’échelle.</t>
+          <t>À une poignée près, tout le monde.</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
+          <t>au moins neuf réponses sur dix sont justes</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Tout le monde a visé beaucoup trop loin.</t>
+          <t>Le cercle est coupé en deux.</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Une partie du cercle était hors sujet.</t>
+          <t>Wow ! Égalité parfaite.</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Collectivement à côté de la plaque.</t>
+          <t>Le cercle est partagé...</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>la moyenne du groupe dépasse le double de la cible</t>
+          <t>les deux options de tête se tiennent à une voix</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Une seule personne talentueuse dans le cercle on dirait.</t>
+          <t>Il y a une option qui devrait finir au feu.</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Une estimation au millimètre dans le lot. Chapeau bas !</t>
+          <t>Il y avait une option de trop on dirait.</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>Il y a un expert dans le cercle. Gardons-le à l'œil !</t>
+          <t>Une proposition délaissée par le cercle.</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Quelqu’un savait, et c'est tout à son honneur.</t>
+          <t>Le cercle n'est pas dûpe face à cette option bancale.</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+          <t>une option n’a recueilli aucune voix</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Le cercle est parti se promener sur cette estimation on dirait.</t>
+          <t>Le cercle est d’accord. C’est rare.</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Alors... le but du jeu c'est d'être le plus proche de la réponse, pas le plus loin.</t>
+          <t>Consensus écrasant.</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Le cercle est resté loin du compte. Il va falloir songer à toucher du bois un peu.</t>
+          <t>Presque tout le cercle est du même avis.</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Ouch ! Le feu se sent bien seul sur celle-là.</t>
+          <t>Le feu s'intensifie en voyant une telle unité !</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+          <t>vote : une option dépasse huit voix sur dix</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Voici un podium de qualité ! (et le reste du cercle aussi vous avez du talent)</t>
+          <t>Le cercle hésite. Deux camps à égalité.</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>La feu a rendu son verdict ! Bravo à notre grand vainqueur !</t>
+          <t>Le feu brûle de bonheur en voyant cette compétition !</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Trois en haut, et tout le monde danse autour du feu.</t>
+          <t>La cercle est coupé en deux... ça fait des demi-cercles du coup.</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+          <t>vote : les deux premières options à une voix près</t>
         </is>
       </c>
     </row>
@@ -3780,22 +3780,422 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
+          <t>Mais qui a gagné en fait ?</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>vote : les deux premières options à une voix près</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>Un cercle de qualité !</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>Ensemble, le cercle a ajusté sa mire !</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle a envoyé du bois sur celle-ci.</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>La sagesse de la foule, pour une fois.</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe est à moins de 10 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle s’est trompé d’échelle.</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>Tout le monde a visé beaucoup trop loin.</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="5" t="inlineStr">
+        <is>
+          <t>Une partie du cercle était hors sujet.</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="5" t="inlineStr">
+        <is>
+          <t>Collectivement à côté de la plaque.</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="inlineStr">
+        <is>
+          <t>la moyenne du groupe dépasse le double de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="5" t="inlineStr">
+        <is>
+          <t>Une seule personne talentueuse dans le cercle on dirait.</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>Une estimation au millimètre dans le lot. Chapeau bas !</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>Il y a un expert dans le cercle. Gardons-le à l'œil !</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
+          <t>Quelqu’un savait, et c'est tout à son honneur.</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="inlineStr">
+        <is>
+          <t>estimation : une seule personne a trouvé la valeur exacte</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle est parti se promener sur cette estimation on dirait.</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="5" t="inlineStr">
+        <is>
+          <t>Alors... le but du jeu c'est d'être le plus proche de la réponse, pas le plus loin.</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="inlineStr">
+        <is>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>Le cercle est resté loin du compte. Il va falloir songer à toucher du bois un peu.</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Ouch ! Le feu se sent bien seul sur celle-là.</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>même la meilleure estimation reste à plus de 50 % de la cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
+          <t>Voici un podium de qualité ! (et le reste du cercle aussi vous avez du talent)</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="5" t="inlineStr">
+        <is>
+          <t>La feu a rendu son verdict ! Bravo à notre grand vainqueur !</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="inlineStr">
+        <is>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="5" t="inlineStr">
+        <is>
+          <t>Trois en haut, et tout le monde danse autour du feu.</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="5" t="inlineStr">
+        <is>
           <t>Tout feu tout flamme ces 3 gagnants ! (et les autres vous êtes chauds aussi !)</t>
         </is>
       </c>
-      <c r="C166" s="4" t="inlineStr">
-        <is>
-          <t>Stream (OBS)</t>
-        </is>
-      </c>
-      <c r="D166" s="5" t="inlineStr">
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>Stream (OBS)</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="inlineStr">
         <is>
           <t>podium affiché — SEUL moment où le stream nomme quelqu’un, pour célébrer</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D166"/>
+  <autoFilter ref="A1:D186"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>